--- a/reporte_Mensajero.xlsx
+++ b/reporte_Mensajero.xlsx
@@ -1811,7 +1811,7 @@
       </c>
       <c r="AI5" s="6" t="inlineStr">
         <is>
-          <t>Oc327865 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
+          <t>OC327865 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ5" s="8" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="AI7" s="6" t="inlineStr">
         <is>
-          <t>Oc327867 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
+          <t>OC327867 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ7" s="8" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="AI9" s="6" t="inlineStr">
         <is>
-          <t>Oc327961 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
+          <t>OC327961 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ9" s="8" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AI10" s="12" t="inlineStr">
         <is>
-          <t>Oc328598 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328598 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ10" s="14" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="AI11" s="6" t="inlineStr">
         <is>
-          <t>Oc328601 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328601 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ11" s="8" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="AI12" s="12" t="inlineStr">
         <is>
-          <t>Oc328602 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328602 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ12" s="14" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="AI13" s="6" t="inlineStr">
         <is>
-          <t>Oc328603 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328603 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ13" s="8" t="inlineStr">
@@ -4839,7 +4839,7 @@
       </c>
       <c r="AI15" s="6" t="inlineStr">
         <is>
-          <t>Oc320754 publicación anterior. Para mayor información relacionada con el proyecto, dirigirse con el lic. Héctor michel, encargado de proyectos.</t>
+          <t>OC320754 publicación anterior. Para mayor información relacionada con el proyecto, dirigirse con el lic. Héctor michel, encargado de proyectos.</t>
         </is>
       </c>
       <c r="AJ15" s="8" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AI16" s="12" t="inlineStr">
         <is>
-          <t>Oc327900 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
+          <t>OC327900 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ16" s="14" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="AI17" s="6" t="inlineStr">
         <is>
-          <t>Oc327901 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
+          <t>OC327901 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ17" s="8" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AI18" s="12" t="inlineStr">
         <is>
-          <t>Oc327836 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
+          <t>OC327836 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ18" s="14" t="inlineStr">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="AI19" s="6" t="inlineStr">
         <is>
-          <t>Oc327868 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
+          <t>OC327868 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ19" s="8" t="inlineStr">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="AI20" s="12" t="inlineStr">
         <is>
-          <t>Oc327866 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
+          <t>OC327866 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ20" s="14" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="AI21" s="6" t="inlineStr">
         <is>
-          <t>Oc327835 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
+          <t>OC327835 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ21" s="8" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="AI22" s="12" t="inlineStr">
         <is>
-          <t>Oc327902 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
+          <t>OC327902 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Ana gabriela durán, encargada de la compra de materiales o con la arq. Guadalupe lizbeth mulato rentería, encargada del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ22" s="14" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="AI33" s="6" t="inlineStr">
         <is>
-          <t>Oc328720 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la arq. Guadalupe rojas, encargada de obra.</t>
+          <t>OC328720 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la arq. Guadalupe rojas, encargada de obra.</t>
         </is>
       </c>
       <c r="AJ33" s="8" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="AI34" s="12" t="inlineStr">
         <is>
-          <t>Oc329174 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329174 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ34" s="14" t="inlineStr">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="AI35" s="6" t="inlineStr">
         <is>
-          <t>Oc329175 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329175 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ35" s="8" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="AI36" s="12" t="inlineStr">
         <is>
-          <t>Oc329176 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329176 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ36" s="14" t="inlineStr">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AI37" s="6" t="inlineStr">
         <is>
-          <t>Oc329570 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329570 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ37" s="8" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="AI38" s="12" t="inlineStr">
         <is>
-          <t>Oc330079 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330079 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ38" s="14" t="inlineStr">
@@ -11957,7 +11957,7 @@
       </c>
       <c r="AI39" s="6" t="inlineStr">
         <is>
-          <t>Oc330076 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330076 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ39" s="8" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="AI40" s="12" t="inlineStr">
         <is>
-          <t>Oc330087 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330087 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ40" s="14" t="inlineStr">
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AI41" s="6" t="inlineStr">
         <is>
-          <t>Oc330088 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330088 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ41" s="8" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="AI42" s="12" t="inlineStr">
         <is>
-          <t>Oc330095 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330095 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ42" s="14" t="inlineStr">
@@ -13141,7 +13141,7 @@
       </c>
       <c r="AI43" s="6" t="inlineStr">
         <is>
-          <t>Oc320096 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC320096 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ43" s="8" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="AI44" s="12" t="inlineStr">
         <is>
-          <t>Oc330097 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330097 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ44" s="14" t="inlineStr">
@@ -13733,7 +13733,7 @@
       </c>
       <c r="AI45" s="6" t="inlineStr">
         <is>
-          <t>Oc330150 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330150 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ45" s="8" t="inlineStr">
@@ -14028,7 +14028,7 @@
       </c>
       <c r="AI46" s="12" t="inlineStr">
         <is>
-          <t>Oc330153 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330153 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ46" s="14" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="AI47" s="6" t="inlineStr">
         <is>
-          <t>Oc330164 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330164 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ47" s="8" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="AI48" s="12" t="inlineStr">
         <is>
-          <t>Oc330164 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330164 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ48" s="14" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="AI49" s="6" t="inlineStr">
         <is>
-          <t>Oc324306 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto.</t>
+          <t>OC324306 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto.</t>
         </is>
       </c>
       <c r="AJ49" s="8" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="AI50" s="12" t="inlineStr">
         <is>
-          <t>Oc324283 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC324283 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ50" s="14" t="inlineStr">
@@ -15507,7 +15507,7 @@
       </c>
       <c r="AI51" s="6" t="inlineStr">
         <is>
-          <t>Oc324307 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC324307 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ51" s="8" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="AI52" s="12" t="inlineStr">
         <is>
-          <t>Oc330174 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330174 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ52" s="14" t="inlineStr">
@@ -16099,7 +16099,7 @@
       </c>
       <c r="AI53" s="6" t="inlineStr">
         <is>
-          <t>Oc330175 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330175 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ53" s="8" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="AI54" s="12" t="inlineStr">
         <is>
-          <t>Oc324308 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto.</t>
+          <t>OC324308 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto.</t>
         </is>
       </c>
       <c r="AJ54" s="14" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="AI55" s="6" t="inlineStr">
         <is>
-          <t>Oc324310 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC324310 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. José efraín cantú maciel, encargado de compras o con el arq. Agustin rodríguez muñoz, encargado del proyecto. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ55" s="8" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="AI58" s="12" t="inlineStr">
         <is>
-          <t>Oc330176 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330176 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ58" s="14" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="AI59" s="6" t="inlineStr">
         <is>
-          <t>Oc330177 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330177 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ59" s="8" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="AI60" s="12" t="inlineStr">
         <is>
-          <t>Oc330178 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330178 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ60" s="14" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="AI61" s="6" t="inlineStr">
         <is>
-          <t>Oc330179 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330179 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ61" s="8" t="inlineStr">
@@ -18762,7 +18762,7 @@
       </c>
       <c r="AI62" s="12" t="inlineStr">
         <is>
-          <t>Oc330185 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330185 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ62" s="14" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="AI63" s="6" t="inlineStr">
         <is>
-          <t>Oc328897 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
+          <t>OC328897 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ63" s="8" t="inlineStr">
@@ -19342,7 +19342,7 @@
       </c>
       <c r="AI64" s="12" t="inlineStr">
         <is>
-          <t>Oc328899 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
+          <t>OC328899 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ64" s="14" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="AI65" s="6" t="inlineStr">
         <is>
-          <t>Oc329179 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329179 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ65" s="8" t="inlineStr">
@@ -19920,7 +19920,7 @@
       </c>
       <c r="AI66" s="12" t="inlineStr">
         <is>
-          <t>Oc328901 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
+          <t>OC328901 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ66" s="14" t="inlineStr">
@@ -20205,7 +20205,7 @@
       </c>
       <c r="AI67" s="6" t="inlineStr">
         <is>
-          <t>Oc329183 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329183 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ67" s="8" t="inlineStr">
@@ -20498,7 +20498,7 @@
       </c>
       <c r="AI68" s="12" t="inlineStr">
         <is>
-          <t>Oc329184 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
+          <t>OC329184 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ68" s="14" t="inlineStr">
@@ -20791,7 +20791,7 @@
       </c>
       <c r="AI69" s="6" t="inlineStr">
         <is>
-          <t>Oc328928 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
+          <t>OC328928 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ69" s="8" t="inlineStr">
@@ -21076,7 +21076,7 @@
       </c>
       <c r="AI70" s="12" t="inlineStr">
         <is>
-          <t>Oc328929 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
+          <t>OC328929 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ70" s="14" t="inlineStr">
@@ -21361,7 +21361,7 @@
       </c>
       <c r="AI71" s="6" t="inlineStr">
         <is>
-          <t>Oc328931 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
+          <t>OC328931 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ71" s="8" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="AI72" s="12" t="inlineStr">
         <is>
-          <t>Oc328932 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
+          <t>OC328932 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. David cuan, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ72" s="14" t="inlineStr">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="AI73" s="6" t="inlineStr">
         <is>
-          <t>Oc329208 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329208 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ73" s="8" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="AI74" s="12" t="inlineStr">
         <is>
-          <t>Oc328915 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328915 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ74" s="14" t="inlineStr">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="AI75" s="6" t="inlineStr">
         <is>
-          <t>Oc329209 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329209 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ75" s="8" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="AI76" s="12" t="inlineStr">
         <is>
-          <t>Oc329210 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329210 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ76" s="14" t="inlineStr">
@@ -23111,7 +23111,7 @@
       </c>
       <c r="AI77" s="6" t="inlineStr">
         <is>
-          <t>Oc328916 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328916 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ77" s="8" t="inlineStr">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AI78" s="12" t="inlineStr">
         <is>
-          <t>Oc328917 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328917 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ78" s="14" t="inlineStr">
@@ -23713,7 +23713,7 @@
       </c>
       <c r="AI79" s="6" t="inlineStr">
         <is>
-          <t>Oc329214 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329214 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ79" s="8" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="AI80" s="12" t="inlineStr">
         <is>
-          <t>Oc328918 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328918 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ80" s="14" t="inlineStr">
@@ -24307,7 +24307,7 @@
       </c>
       <c r="AI81" s="6" t="inlineStr">
         <is>
-          <t>Oc330185 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330185 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ81" s="8" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="AI82" s="12" t="inlineStr">
         <is>
-          <t>Oc328919 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328919 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ82" s="14" t="inlineStr">
@@ -24903,7 +24903,7 @@
       </c>
       <c r="AI83" s="6" t="inlineStr">
         <is>
-          <t>Oc328961 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328961 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ83" s="8" t="inlineStr">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="AI84" s="12" t="inlineStr">
         <is>
-          <t>Oc330191 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330191 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ84" s="14" t="inlineStr">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="AI85" s="6" t="inlineStr">
         <is>
-          <t>Oc328963 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328963 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ85" s="8" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="AI86" s="12" t="inlineStr">
         <is>
-          <t>Oc328805 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328805 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ86" s="14" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="AI87" s="6" t="inlineStr">
         <is>
-          <t>Oc328808 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328808 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ87" s="8" t="inlineStr">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="AI88" s="12" t="inlineStr">
         <is>
-          <t>Oc328843 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328843 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ88" s="14" t="inlineStr">
@@ -26727,7 +26727,7 @@
       </c>
       <c r="AI89" s="6" t="inlineStr">
         <is>
-          <t>Oc328876 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328876 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ89" s="8" t="inlineStr">
@@ -27036,7 +27036,7 @@
       </c>
       <c r="AI90" s="12" t="inlineStr">
         <is>
-          <t>Oc330193 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330193 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ90" s="14" t="inlineStr">
@@ -27331,7 +27331,7 @@
       </c>
       <c r="AI91" s="6" t="inlineStr">
         <is>
-          <t>Oc330199 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330199 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ91" s="8" t="inlineStr">
@@ -27626,7 +27626,7 @@
       </c>
       <c r="AI92" s="12" t="inlineStr">
         <is>
-          <t>Oc328811 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328811 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ92" s="14" t="inlineStr">
@@ -27935,7 +27935,7 @@
       </c>
       <c r="AI93" s="6" t="inlineStr">
         <is>
-          <t>Oc328444 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328444 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ93" s="8" t="inlineStr">
@@ -28244,7 +28244,7 @@
       </c>
       <c r="AI94" s="12" t="inlineStr">
         <is>
-          <t>Oc328845 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328845 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ94" s="14" t="inlineStr">
@@ -28553,7 +28553,7 @@
       </c>
       <c r="AI95" s="6" t="inlineStr">
         <is>
-          <t>Oc328846 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC328846 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Javier méndez bocanegra, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ95" s="8" t="inlineStr">
@@ -28862,7 +28862,7 @@
       </c>
       <c r="AI96" s="12" t="inlineStr">
         <is>
-          <t>Oc330198 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330198 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ96" s="14" t="inlineStr">
@@ -29157,7 +29157,7 @@
       </c>
       <c r="AI97" s="6" t="inlineStr">
         <is>
-          <t>Oc330200 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330200 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ97" s="8" t="inlineStr">
@@ -29452,7 +29452,7 @@
       </c>
       <c r="AI98" s="12" t="inlineStr">
         <is>
-          <t>Oc328965 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328965 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ98" s="14" t="inlineStr">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="AI99" s="6" t="inlineStr">
         <is>
-          <t>Oc330201 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330201 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ99" s="8" t="inlineStr">
@@ -30048,7 +30048,7 @@
       </c>
       <c r="AI100" s="12" t="inlineStr">
         <is>
-          <t>Oc328970 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328970 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el lic. Miguel cedillo, encargado de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ100" s="14" t="inlineStr">
@@ -30349,7 +30349,7 @@
       </c>
       <c r="AI101" s="6" t="inlineStr">
         <is>
-          <t>Oc330202 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330202 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ101" s="8" t="inlineStr">
@@ -30644,7 +30644,7 @@
       </c>
       <c r="AI102" s="12" t="inlineStr">
         <is>
-          <t>Oc330203 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330203 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ102" s="14" t="inlineStr">
@@ -30939,7 +30939,7 @@
       </c>
       <c r="AI103" s="6" t="inlineStr">
         <is>
-          <t>Oc328767 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Roberto antonio pimentel torres, encargado de la obra y de la compra de materiales.</t>
+          <t>OC328767 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Roberto antonio pimentel torres, encargado de la obra y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ103" s="8" t="inlineStr">
@@ -31228,7 +31228,7 @@
       </c>
       <c r="AI104" s="12" t="inlineStr">
         <is>
-          <t>Oc328766 publicación anterior. Habifel subcontrata la mano de obra y compra parte de los materiales. Para mayor información relacionado al proyecto, dirigirse con el arq. Hugo tow, encargado del proyecto.</t>
+          <t>OC328766 publicación anterior. Habifel subcontrata la mano de obra y compra parte de los materiales. Para mayor información relacionado al proyecto, dirigirse con el arq. Hugo tow, encargado del proyecto.</t>
         </is>
       </c>
       <c r="AJ104" s="14" t="inlineStr">
@@ -31513,7 +31513,7 @@
       </c>
       <c r="AI105" s="6" t="inlineStr">
         <is>
-          <t>Oc330095 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
+          <t>OC330095 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Cindy hernández, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ105" s="8" t="inlineStr">
@@ -31808,7 +31808,7 @@
       </c>
       <c r="AI106" s="12" t="inlineStr">
         <is>
-          <t>Oc329224 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329224 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ106" s="14" t="inlineStr">
@@ -32101,7 +32101,7 @@
       </c>
       <c r="AI107" s="6" t="inlineStr">
         <is>
-          <t>Oc329227 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329227 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ107" s="8" t="inlineStr">
@@ -32394,7 +32394,7 @@
       </c>
       <c r="AI108" s="12" t="inlineStr">
         <is>
-          <t>Oc329228 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329228 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ108" s="14" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="AI110" s="12" t="inlineStr">
         <is>
-          <t>Oc329229 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329229 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ110" s="14" t="inlineStr">
@@ -33263,7 +33263,7 @@
       </c>
       <c r="AI111" s="6" t="inlineStr">
         <is>
-          <t>Oc329243 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329243 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ111" s="8" t="inlineStr">
@@ -33556,7 +33556,7 @@
       </c>
       <c r="AI112" s="12" t="inlineStr">
         <is>
-          <t>Oc329244 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329244 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ112" s="14" t="inlineStr">
@@ -33849,7 +33849,7 @@
       </c>
       <c r="AI113" s="6" t="inlineStr">
         <is>
-          <t>Oc329246 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329246 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ113" s="8" t="inlineStr">
@@ -34142,7 +34142,7 @@
       </c>
       <c r="AI114" s="12" t="inlineStr">
         <is>
-          <t>Oc329263 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329263 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ114" s="14" t="inlineStr">
@@ -34433,7 +34433,7 @@
       </c>
       <c r="AI115" s="6" t="inlineStr">
         <is>
-          <t>Oc328787 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Gregorio pérez, encargado de la obra.</t>
+          <t>OC328787 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Gregorio pérez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ115" s="8" t="inlineStr">
@@ -34732,7 +34732,7 @@
       </c>
       <c r="AI116" s="12" t="inlineStr">
         <is>
-          <t>Oc329265 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
+          <t>OC329265 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras.</t>
         </is>
       </c>
       <c r="AJ116" s="14" t="inlineStr">
@@ -35025,7 +35025,7 @@
       </c>
       <c r="AI117" s="6" t="inlineStr">
         <is>
-          <t>Oc326557 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Karla roman, encargada de la compra de materiales o con la arq. Candelaria rios, encargada del proyecto.</t>
+          <t>OC326557 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Karla roman, encargada de la compra de materiales o con la arq. Candelaria rios, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ117" s="8" t="inlineStr">
@@ -35316,7 +35316,7 @@
       </c>
       <c r="AI118" s="12" t="inlineStr">
         <is>
-          <t>Oc326559 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Karla roman, encargada de la compra de materiales o con la arq. Candelaria rios, encargada del proyecto.</t>
+          <t>OC326559 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Karla roman, encargada de la compra de materiales o con la arq. Candelaria rios, encargada del proyecto.</t>
         </is>
       </c>
       <c r="AJ118" s="14" t="inlineStr">
@@ -35607,7 +35607,7 @@
       </c>
       <c r="AI119" s="6" t="inlineStr">
         <is>
-          <t>Oc329284 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
+          <t>OC329284 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ119" s="8" t="inlineStr">
@@ -35900,7 +35900,7 @@
       </c>
       <c r="AI120" s="12" t="inlineStr">
         <is>
-          <t>Oc328785 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Gregorio pérez, encargado de la obra. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328785 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Gregorio pérez, encargado de la obra. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ120" s="14" t="inlineStr">
@@ -36201,7 +36201,7 @@
       </c>
       <c r="AI121" s="6" t="inlineStr">
         <is>
-          <t>Oc329285 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
+          <t>OC329285 publicación anterior. Inmobiliaria ruba realiza las negociaciones con los proveedores y subcontrata la mano de obra. Para mayor información relacionado al proyecto, dirigirse con el ing. Jorge pérez, encargado del proyecto y de compras. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ121" s="8" t="inlineStr">
@@ -36785,7 +36785,7 @@
       </c>
       <c r="AI123" s="6" t="inlineStr">
         <is>
-          <t>Oc327550 publicación anterior. Constructora lodela subcontratará parte de la obra y compra parte de los materiales. Para mayor información relacionado al proyecto, dirigirse con el ing. Adrian sarmiento, encargado de compras.</t>
+          <t>OC327550 publicación anterior. Constructora lodela subcontratará parte de la obra y compra parte de los materiales. Para mayor información relacionado al proyecto, dirigirse con el ing. Adrian sarmiento, encargado de compras.</t>
         </is>
       </c>
       <c r="AJ123" s="8" t="inlineStr">
@@ -37373,7 +37373,7 @@
       </c>
       <c r="AI125" s="6" t="inlineStr">
         <is>
-          <t>Oc328702 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la arq. Esperanza jiménez, encargada de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328702 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la arq. Esperanza jiménez, encargada de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ125" s="8" t="inlineStr">
@@ -37666,7 +37666,7 @@
       </c>
       <c r="AI126" s="12" t="inlineStr">
         <is>
-          <t>Oc327219 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Israel vargas ortega, encargado del proyecto o con el arq. Pedro muñoz garcia, encargado de la compra de materiales.</t>
+          <t>OC327219 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el arq. Israel vargas ortega, encargado del proyecto o con el arq. Pedro muñoz garcia, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ126" s="14" t="inlineStr">
@@ -37969,7 +37969,7 @@
       </c>
       <c r="AI127" s="6" t="inlineStr">
         <is>
-          <t>Oc326367 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el arq. José luis medina armas, encargado del proyecto y de la compra de materiales.</t>
+          <t>OC326367 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el arq. José luis medina armas, encargado del proyecto y de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ127" s="8" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AI129" s="6" t="inlineStr">
         <is>
-          <t>Oc326467 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Kabir rodríguez o con la arq. Sofia huerta, encargados del proyecto y de la compra de materiales. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC326467 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Kabir rodríguez o con la arq. Sofia huerta, encargados del proyecto y de la compra de materiales. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ129" s="8" t="inlineStr">
@@ -38838,7 +38838,7 @@
       </c>
       <c r="AI130" s="12" t="inlineStr">
         <is>
-          <t>Oc328511 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Martha ramírez, encargada de la compra de materiales.</t>
+          <t>OC328511 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Martha ramírez, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ130" s="14" t="inlineStr">
@@ -39430,7 +39430,7 @@
       </c>
       <c r="AI132" s="12" t="inlineStr">
         <is>
-          <t>Oc328510 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Martha ramírez, encargada de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328510 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Martha ramírez, encargada de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ132" s="14" t="inlineStr">
@@ -39721,7 +39721,7 @@
       </c>
       <c r="AI133" s="6" t="inlineStr">
         <is>
-          <t>Oc328512 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Martha ramírez, encargada de la compra de materiales.</t>
+          <t>OC328512 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Martha ramírez, encargada de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ133" s="8" t="inlineStr">
@@ -40012,7 +40012,7 @@
       </c>
       <c r="AI134" s="12" t="inlineStr">
         <is>
-          <t>Oc328390 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el lic. Manuel calderón, encargado de costos.</t>
+          <t>OC328390 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el lic. Manuel calderón, encargado de costos.</t>
         </is>
       </c>
       <c r="AJ134" s="14" t="inlineStr">
@@ -40313,7 +40313,7 @@
       </c>
       <c r="AI135" s="6" t="inlineStr">
         <is>
-          <t>Oc328396 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el lic. Manuel calderón, encargado de costos.</t>
+          <t>OC328396 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el lic. Manuel calderón, encargado de costos.</t>
         </is>
       </c>
       <c r="AJ135" s="8" t="inlineStr">
@@ -40614,7 +40614,7 @@
       </c>
       <c r="AI136" s="12" t="inlineStr">
         <is>
-          <t>Oc328393 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el lic. Manuel calderón, encargado de costos.</t>
+          <t>OC328393 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el lic. Manuel calderón, encargado de costos.</t>
         </is>
       </c>
       <c r="AJ136" s="14" t="inlineStr">
@@ -40915,7 +40915,7 @@
       </c>
       <c r="AI137" s="6" t="inlineStr">
         <is>
-          <t>Oc328378 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la obra.</t>
+          <t>OC328378 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ137" s="8" t="inlineStr">
@@ -41216,7 +41216,7 @@
       </c>
       <c r="AI138" s="12" t="inlineStr">
         <is>
-          <t>Oc328379 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la obra.</t>
+          <t>OC328379 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ138" s="14" t="inlineStr">
@@ -41515,7 +41515,7 @@
       </c>
       <c r="AI139" s="6" t="inlineStr">
         <is>
-          <t>Oc328353 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la obra.</t>
+          <t>OC328353 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ139" s="8" t="inlineStr">
@@ -41816,7 +41816,7 @@
       </c>
       <c r="AI140" s="12" t="inlineStr">
         <is>
-          <t>Oc328354 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José angel cardenas, encargado de la obra.</t>
+          <t>OC328354 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José angel cardenas, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ140" s="14" t="inlineStr">
@@ -42115,7 +42115,7 @@
       </c>
       <c r="AI141" s="6" t="inlineStr">
         <is>
-          <t>Oc328294 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Elba naranjo gonzález, encargada del proyecto y de la compra de materiales. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulaciòn.</t>
+          <t>OC328294 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con la lic. Elba naranjo gonzález, encargada del proyecto y de la compra de materiales. La superficie total a construir contiene la zona habitable, mas un 20% de superficie cubierta que corresponde a areas comunes, de servicios y circulaciòn.</t>
         </is>
       </c>
       <c r="AJ141" s="8" t="inlineStr">
@@ -42400,7 +42400,7 @@
       </c>
       <c r="AI142" s="12" t="inlineStr">
         <is>
-          <t>Oc328347 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José angel cardenas, encargado de la obra.</t>
+          <t>OC328347 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José angel cardenas, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ142" s="14" t="inlineStr">
@@ -42699,7 +42699,7 @@
       </c>
       <c r="AI143" s="6" t="inlineStr">
         <is>
-          <t>Oc328348 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328348 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ143" s="8" t="inlineStr">
@@ -42998,7 +42998,7 @@
       </c>
       <c r="AI144" s="12" t="inlineStr">
         <is>
-          <t>Oc328440 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328440 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ144" s="14" t="inlineStr">
@@ -43291,7 +43291,7 @@
       </c>
       <c r="AI145" s="6" t="inlineStr">
         <is>
-          <t>Oc328441 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328441 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ145" s="8" t="inlineStr">
@@ -43584,7 +43584,7 @@
       </c>
       <c r="AI146" s="12" t="inlineStr">
         <is>
-          <t>Oc328355 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
+          <t>OC328355 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. José ángel cárdenas, encargado de la compra de materiales. La superficie total a construir contiene la zona habitable, más un 20% de superficie cubierta que corresponde a áreas comunes, de servicios y circulación.</t>
         </is>
       </c>
       <c r="AJ146" s="14" t="inlineStr">
@@ -43883,7 +43883,7 @@
       </c>
       <c r="AI147" s="6" t="inlineStr">
         <is>
-          <t>Oc328374 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328374 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ147" s="8" t="inlineStr">
@@ -44176,7 +44176,7 @@
       </c>
       <c r="AI148" s="12" t="inlineStr">
         <is>
-          <t>Oc328375 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328375 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ148" s="14" t="inlineStr">
@@ -44469,7 +44469,7 @@
       </c>
       <c r="AI149" s="6" t="inlineStr">
         <is>
-          <t>Oc328413 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328413 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ149" s="8" t="inlineStr">
@@ -45059,7 +45059,7 @@
       </c>
       <c r="AI151" s="6" t="inlineStr">
         <is>
-          <t>Oc321332 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Horacio vázquez, encargado de la obra.</t>
+          <t>OC321332 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Horacio vázquez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ151" s="8" t="inlineStr">
@@ -45348,7 +45348,7 @@
       </c>
       <c r="AI152" s="12" t="inlineStr">
         <is>
-          <t>Oc328349 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328349 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ152" s="14" t="inlineStr">
@@ -45641,7 +45641,7 @@
       </c>
       <c r="AI153" s="6" t="inlineStr">
         <is>
-          <t>Oc328350 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328350 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ153" s="8" t="inlineStr">
@@ -45934,7 +45934,7 @@
       </c>
       <c r="AI154" s="12" t="inlineStr">
         <is>
-          <t>Oc328412 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
+          <t>OC328412 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Aarón aguilar santamaria, encargado de la compra de materiales.</t>
         </is>
       </c>
       <c r="AJ154" s="14" t="inlineStr">
@@ -46526,7 +46526,7 @@
       </c>
       <c r="AI156" s="12" t="inlineStr">
         <is>
-          <t>Oc328339 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. Ricardo del prado gutierrez, encargado de compras, comunicarse directamente a su teléfono personal: 2225798019.</t>
+          <t>OC328339 publicación anterior. Para mayor información relacionada al proyecto, dirigirse con el ing. Ricardo del prado gutierrez, encargado de compras, comunicarse directamente a su teléfono personal: 2225798019.</t>
         </is>
       </c>
       <c r="AJ156" s="14" t="inlineStr">
@@ -46811,7 +46811,7 @@
       </c>
       <c r="AI157" s="6" t="inlineStr">
         <is>
-          <t>Oc328641 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328641 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ157" s="8" t="inlineStr">
@@ -47116,7 +47116,7 @@
       </c>
       <c r="AI158" s="12" t="inlineStr">
         <is>
-          <t>Oc328642 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328642 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ158" s="14" t="inlineStr">
@@ -47421,7 +47421,7 @@
       </c>
       <c r="AI159" s="6" t="inlineStr">
         <is>
-          <t>Oc328643 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328643 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ159" s="8" t="inlineStr">
@@ -47726,7 +47726,7 @@
       </c>
       <c r="AI160" s="12" t="inlineStr">
         <is>
-          <t>Oc328648 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328648 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ160" s="14" t="inlineStr">
@@ -48031,7 +48031,7 @@
       </c>
       <c r="AI161" s="6" t="inlineStr">
         <is>
-          <t>Oc328647 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328647 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ161" s="8" t="inlineStr">
@@ -48338,7 +48338,7 @@
       </c>
       <c r="AI162" s="12" t="inlineStr">
         <is>
-          <t>Oc328630 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328630 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ162" s="14" t="inlineStr">
@@ -48645,7 +48645,7 @@
       </c>
       <c r="AI163" s="6" t="inlineStr">
         <is>
-          <t>Oc328631 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328631 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ163" s="8" t="inlineStr">
@@ -48950,7 +48950,7 @@
       </c>
       <c r="AI164" s="12" t="inlineStr">
         <is>
-          <t>Oc328632 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328632 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ164" s="14" t="inlineStr">
@@ -49257,7 +49257,7 @@
       </c>
       <c r="AI165" s="6" t="inlineStr">
         <is>
-          <t>Oc328633 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328633 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ165" s="8" t="inlineStr">
@@ -49562,7 +49562,7 @@
       </c>
       <c r="AI166" s="12" t="inlineStr">
         <is>
-          <t>Oc328634 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328634 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ166" s="14" t="inlineStr">
@@ -49869,7 +49869,7 @@
       </c>
       <c r="AI167" s="6" t="inlineStr">
         <is>
-          <t>Oc328635 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328635 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ167" s="8" t="inlineStr">
@@ -50174,7 +50174,7 @@
       </c>
       <c r="AI168" s="12" t="inlineStr">
         <is>
-          <t>Oc328640 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
+          <t>OC328640 publicación anterior. Para mayor información relacionado al proyecto, dirigirse con el ing. Carlos lópez, encargado de la obra.</t>
         </is>
       </c>
       <c r="AJ168" s="14" t="inlineStr">
